--- a/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,57</t>
+          <t>-0,66; 1,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,96; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,29</t>
+          <t>-1,29; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,39</t>
+          <t>-1,04; 0,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,52</t>
+          <t>-0,85; 0,51</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,0</t>
+          <t>-0,82; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,41</t>
+          <t>-0,17; 1,27</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,61</t>
+          <t>-1,04; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,0</t>
+          <t>-1,61; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,44</t>
+          <t>-0,67; 0,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,1</t>
+          <t>-0,17; 0,94</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,4</t>
+          <t>-0,26; 0,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,75</t>
+          <t>-0,14; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,07</t>
+          <t>-0,68; 0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,57</t>
+          <t>-0,39; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,16</t>
+          <t>-0,37; 0,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,49</t>
+          <t>-0,17; 0,49</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 202,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 648,18</t>
+          <t>-60,3; 502,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -787,27 +787,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,29</t>
+          <t>-0,65; 1,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,31; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,28</t>
+          <t>-1,31; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,42</t>
+          <t>-1,12; 0,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,59</t>
+          <t>-0,99; 0,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,88; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,27</t>
+          <t>-0,17; 1,14</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,6</t>
+          <t>-1,05; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,3</t>
+          <t>-0,52; 0,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,94</t>
+          <t>-0,17; 1,09</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,44</t>
+          <t>-0,26; 0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,7</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,07</t>
+          <t>-0,67; 0,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,53</t>
+          <t>-0,4; 0,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,13</t>
+          <t>-0,38; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,49</t>
+          <t>-0,18; 0,47</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 202,88</t>
+          <t>-100,0; 192,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 502,34</t>
+          <t>-62,09; 505,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,6</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,0</t>
+          <t>-1,31; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,0</t>
+          <t>-0,66; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,28</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,43</t>
+          <t>-1,01; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,51</t>
+          <t>-0,83; 0,52</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>95,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,03</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,6</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>-1,01; 0,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,77; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,14</t>
+          <t>-0,15; 1,41</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-10,28%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,74</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,01; 0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>-1,53; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,3</t>
+          <t>-0,5; 0,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,09</t>
+          <t>-0,32; 1,1</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,52%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,37</t>
+          <t>-0,76; 0,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,72</t>
+          <t>-0,47; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,08</t>
+          <t>-0,28; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,55</t>
+          <t>-0,15; 0,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,12</t>
+          <t>-0,34; 0,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,47</t>
+          <t>-0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-71,11%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>16,05%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>131,08%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-71,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 192,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 505,12</t>
+          <t>-51,25; 648,18</t>
         </is>
       </c>
     </row>
